--- a/invoicing/templates/HDR_template.xlsx
+++ b/invoicing/templates/HDR_template.xlsx
@@ -2811,10 +2811,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" s="16" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="60">
-        <f>'Invoice Summary'!B1</f>
-        <v>0</v>
-      </c>
+      <c r="A1"/>
       <c r="L1" s="17"/>
       <c r="M1" s="17"/>
       <c r="N1" s="17"/>
